--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_364_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_364_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>17</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>15</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>3</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>2</v>
@@ -1727,16 +1727,16 @@
         <v>35</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>13</v>
@@ -1923,10 +1923,10 @@
         <v>16</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>2</v>
@@ -2315,7 +2315,7 @@
         <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2511,10 +2511,10 @@
         <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2710,13 +2710,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>4</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>141</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>38</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>1</v>
@@ -4684,10 +4684,10 @@
         <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5275,13 +5275,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X40" t="n">
         <v>6</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5860,10 +5860,10 @@
         <v>11</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6588,16 +6588,16 @@
         <v>81</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X47" t="n">
         <v>28</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_364_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_364_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
         <v>8</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>88.37</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
         <v>11</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1543,10 +1543,10 @@
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -1739,14 +1739,14 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2131,14 +2131,14 @@
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2719,10 +2719,10 @@
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3839,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5284,10 +5284,10 @@
         <v>3</v>
       </c>
       <c r="X40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6600,14 +6600,14 @@
         <v>4</v>
       </c>
       <c r="X47" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="Y47" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA47" t="n">
